--- a/03_Outputs/Agroindustrial_Occidente/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/03_Ordenamiento/ordenamiento.xlsx
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="E2" s="112">
-        <v>0.580964565312986</v>
+        <v>0.580964565312987</v>
       </c>
     </row>
     <row r="3">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.490477316590846</v>
+        <v>0.490477316590845</v>
       </c>
     </row>
     <row r="4">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="E6" s="112">
-        <v>0.464104800529024</v>
+        <v>0.464104800529025</v>
       </c>
     </row>
     <row r="7">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="E7" s="112">
-        <v>0.37682808037146</v>
+        <v>0.376828080371461</v>
       </c>
     </row>
   </sheetData>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.580964565312986</v>
+        <v>0.580964565312987</v>
       </c>
     </row>
     <row r="3">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.490477316590846</v>
+        <v>0.490477316590845</v>
       </c>
     </row>
     <row r="4">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.464104800529024</v>
+        <v>0.464104800529025</v>
       </c>
     </row>
     <row r="5">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.37682808037146</v>
+        <v>0.376828080371461</v>
       </c>
     </row>
   </sheetData>
